--- a/downloads/receipts.xlsx
+++ b/downloads/receipts.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Receipts" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="343">
   <si>
     <t>expense_id</t>
   </si>
@@ -1482,6 +1482,15 @@
       <c r="H2" t="s">
         <v>18</v>
       </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1508,6 +1517,15 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1534,6 +1552,15 @@
       <c r="H4" t="s">
         <v>18</v>
       </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1560,6 +1587,15 @@
       <c r="H5" t="s">
         <v>18</v>
       </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1586,6 +1622,15 @@
       <c r="H6" t="s">
         <v>18</v>
       </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1612,6 +1657,15 @@
       <c r="H7" t="s">
         <v>18</v>
       </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1638,6 +1692,15 @@
       <c r="H8" t="s">
         <v>18</v>
       </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1664,6 +1727,15 @@
       <c r="H9" t="s">
         <v>18</v>
       </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1690,6 +1762,15 @@
       <c r="H10" t="s">
         <v>18</v>
       </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1716,6 +1797,15 @@
       <c r="H11" t="s">
         <v>18</v>
       </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1742,6 +1832,15 @@
       <c r="H12" t="s">
         <v>18</v>
       </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1768,6 +1867,15 @@
       <c r="H13" t="s">
         <v>18</v>
       </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1794,6 +1902,15 @@
       <c r="H14" t="s">
         <v>18</v>
       </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1820,6 +1937,15 @@
       <c r="H15" t="s">
         <v>18</v>
       </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1846,6 +1972,15 @@
       <c r="H16" t="s">
         <v>18</v>
       </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1872,6 +2007,15 @@
       <c r="H17" t="s">
         <v>18</v>
       </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -1898,6 +2042,15 @@
       <c r="H18" t="s">
         <v>18</v>
       </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -1924,6 +2077,15 @@
       <c r="H19" t="s">
         <v>18</v>
       </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -1950,6 +2112,15 @@
       <c r="H20" t="s">
         <v>18</v>
       </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -1976,6 +2147,15 @@
       <c r="H21" t="s">
         <v>18</v>
       </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -2002,6 +2182,15 @@
       <c r="H22" t="s">
         <v>18</v>
       </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -2028,6 +2217,15 @@
       <c r="H23" t="s">
         <v>18</v>
       </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -2054,6 +2252,15 @@
       <c r="H24" t="s">
         <v>18</v>
       </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -2080,6 +2287,15 @@
       <c r="H25" t="s">
         <v>18</v>
       </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -2106,6 +2322,15 @@
       <c r="H26" t="s">
         <v>18</v>
       </c>
+      <c r="I26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -2132,6 +2357,15 @@
       <c r="H27" t="s">
         <v>18</v>
       </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -2158,6 +2392,15 @@
       <c r="H28" t="s">
         <v>18</v>
       </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -2184,6 +2427,15 @@
       <c r="H29" t="s">
         <v>18</v>
       </c>
+      <c r="I29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K29" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -2210,6 +2462,15 @@
       <c r="H30" t="s">
         <v>18</v>
       </c>
+      <c r="I30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s">
+        <v>18</v>
+      </c>
+      <c r="K30" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -2236,6 +2497,15 @@
       <c r="H31" t="s">
         <v>18</v>
       </c>
+      <c r="I31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s">
+        <v>18</v>
+      </c>
+      <c r="K31" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -2262,6 +2532,15 @@
       <c r="H32" t="s">
         <v>18</v>
       </c>
+      <c r="I32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" t="s">
+        <v>18</v>
+      </c>
+      <c r="K32" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -2288,6 +2567,15 @@
       <c r="H33" t="s">
         <v>18</v>
       </c>
+      <c r="I33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -2314,6 +2602,15 @@
       <c r="H34" t="s">
         <v>18</v>
       </c>
+      <c r="I34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -2340,6 +2637,15 @@
       <c r="H35" t="s">
         <v>18</v>
       </c>
+      <c r="I35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -2366,6 +2672,15 @@
       <c r="H36" t="s">
         <v>18</v>
       </c>
+      <c r="I36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -2392,6 +2707,15 @@
       <c r="H37" t="s">
         <v>18</v>
       </c>
+      <c r="I37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" t="s">
+        <v>18</v>
+      </c>
+      <c r="K37" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -2418,6 +2742,15 @@
       <c r="H38" t="s">
         <v>18</v>
       </c>
+      <c r="I38" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" t="s">
+        <v>18</v>
+      </c>
+      <c r="K38" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -2444,6 +2777,15 @@
       <c r="H39" t="s">
         <v>18</v>
       </c>
+      <c r="I39" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" t="s">
+        <v>18</v>
+      </c>
+      <c r="K39" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -2470,6 +2812,15 @@
       <c r="H40" t="s">
         <v>18</v>
       </c>
+      <c r="I40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -2496,6 +2847,15 @@
       <c r="H41" t="s">
         <v>18</v>
       </c>
+      <c r="I41" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" t="s">
+        <v>18</v>
+      </c>
+      <c r="K41" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -2522,6 +2882,15 @@
       <c r="H42" t="s">
         <v>18</v>
       </c>
+      <c r="I42" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" t="s">
+        <v>18</v>
+      </c>
+      <c r="K42" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -2548,6 +2917,15 @@
       <c r="H43" t="s">
         <v>18</v>
       </c>
+      <c r="I43" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -2574,6 +2952,15 @@
       <c r="H44" t="s">
         <v>18</v>
       </c>
+      <c r="I44" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" t="s">
+        <v>18</v>
+      </c>
+      <c r="K44" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -2600,6 +2987,15 @@
       <c r="H45" t="s">
         <v>18</v>
       </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" t="s">
+        <v>18</v>
+      </c>
+      <c r="K45" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -2626,6 +3022,15 @@
       <c r="H46" t="s">
         <v>18</v>
       </c>
+      <c r="I46" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" t="s">
+        <v>18</v>
+      </c>
+      <c r="K46" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -2652,6 +3057,15 @@
       <c r="H47" t="s">
         <v>18</v>
       </c>
+      <c r="I47" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" t="s">
+        <v>18</v>
+      </c>
+      <c r="K47" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -2678,6 +3092,15 @@
       <c r="H48" t="s">
         <v>18</v>
       </c>
+      <c r="I48" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" t="s">
+        <v>18</v>
+      </c>
+      <c r="K48" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -2704,6 +3127,15 @@
       <c r="H49" t="s">
         <v>18</v>
       </c>
+      <c r="I49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" t="s">
+        <v>18</v>
+      </c>
+      <c r="K49" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -2730,6 +3162,15 @@
       <c r="H50" t="s">
         <v>18</v>
       </c>
+      <c r="I50" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" t="s">
+        <v>18</v>
+      </c>
+      <c r="K50" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -2756,6 +3197,15 @@
       <c r="H51" t="s">
         <v>18</v>
       </c>
+      <c r="I51" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" t="s">
+        <v>18</v>
+      </c>
+      <c r="K51" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -2782,6 +3232,15 @@
       <c r="H52" t="s">
         <v>18</v>
       </c>
+      <c r="I52" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" t="s">
+        <v>18</v>
+      </c>
+      <c r="K52" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2808,6 +3267,15 @@
       <c r="H53" t="s">
         <v>18</v>
       </c>
+      <c r="I53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" t="s">
+        <v>18</v>
+      </c>
+      <c r="K53" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -2834,6 +3302,15 @@
       <c r="H54" t="s">
         <v>18</v>
       </c>
+      <c r="I54" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" t="s">
+        <v>18</v>
+      </c>
+      <c r="K54" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -2860,6 +3337,15 @@
       <c r="H55" t="s">
         <v>18</v>
       </c>
+      <c r="I55" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s">
+        <v>18</v>
+      </c>
+      <c r="K55" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
@@ -2886,6 +3372,15 @@
       <c r="H56" t="s">
         <v>18</v>
       </c>
+      <c r="I56" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" t="s">
+        <v>18</v>
+      </c>
+      <c r="K56" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -2912,6 +3407,15 @@
       <c r="H57" t="s">
         <v>18</v>
       </c>
+      <c r="I57" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" t="s">
+        <v>18</v>
+      </c>
+      <c r="K57" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -2938,6 +3442,15 @@
       <c r="H58" t="s">
         <v>18</v>
       </c>
+      <c r="I58" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" t="s">
+        <v>18</v>
+      </c>
+      <c r="K58" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -2964,6 +3477,15 @@
       <c r="H59" t="s">
         <v>18</v>
       </c>
+      <c r="I59" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" t="s">
+        <v>18</v>
+      </c>
+      <c r="K59" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -2990,6 +3512,15 @@
       <c r="H60" t="s">
         <v>18</v>
       </c>
+      <c r="I60" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K60" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -3016,6 +3547,15 @@
       <c r="H61" t="s">
         <v>18</v>
       </c>
+      <c r="I61" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" t="s">
+        <v>18</v>
+      </c>
+      <c r="K61" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -3042,6 +3582,15 @@
       <c r="H62" t="s">
         <v>18</v>
       </c>
+      <c r="I62" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" t="s">
+        <v>18</v>
+      </c>
+      <c r="K62" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -3068,6 +3617,15 @@
       <c r="H63" t="s">
         <v>18</v>
       </c>
+      <c r="I63" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" t="s">
+        <v>18</v>
+      </c>
+      <c r="K63" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -3094,6 +3652,15 @@
       <c r="H64" t="s">
         <v>18</v>
       </c>
+      <c r="I64" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" t="s">
+        <v>18</v>
+      </c>
+      <c r="K64" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
@@ -3120,6 +3687,15 @@
       <c r="H65" t="s">
         <v>18</v>
       </c>
+      <c r="I65" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" t="s">
+        <v>18</v>
+      </c>
+      <c r="K65" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
@@ -3146,6 +3722,15 @@
       <c r="H66" t="s">
         <v>18</v>
       </c>
+      <c r="I66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" t="s">
+        <v>18</v>
+      </c>
+      <c r="K66" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -3172,6 +3757,15 @@
       <c r="H67" t="s">
         <v>18</v>
       </c>
+      <c r="I67" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" t="s">
+        <v>18</v>
+      </c>
+      <c r="K67" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -3198,6 +3792,15 @@
       <c r="H68" t="s">
         <v>18</v>
       </c>
+      <c r="I68" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" t="s">
+        <v>18</v>
+      </c>
+      <c r="K68" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -3224,6 +3827,15 @@
       <c r="H69" t="s">
         <v>18</v>
       </c>
+      <c r="I69" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" t="s">
+        <v>18</v>
+      </c>
+      <c r="K69" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -3250,6 +3862,15 @@
       <c r="H70" t="s">
         <v>18</v>
       </c>
+      <c r="I70" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" t="s">
+        <v>18</v>
+      </c>
+      <c r="K70" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -3276,6 +3897,15 @@
       <c r="H71" t="s">
         <v>18</v>
       </c>
+      <c r="I71" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" t="s">
+        <v>18</v>
+      </c>
+      <c r="K71" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -3302,6 +3932,15 @@
       <c r="H72" t="s">
         <v>18</v>
       </c>
+      <c r="I72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s">
+        <v>18</v>
+      </c>
+      <c r="K72" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -3328,6 +3967,15 @@
       <c r="H73" t="s">
         <v>18</v>
       </c>
+      <c r="I73" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" t="s">
+        <v>18</v>
+      </c>
+      <c r="K73" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
@@ -3354,6 +4002,15 @@
       <c r="H74" t="s">
         <v>18</v>
       </c>
+      <c r="I74" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" t="s">
+        <v>18</v>
+      </c>
+      <c r="K74" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -3380,6 +4037,15 @@
       <c r="H75" t="s">
         <v>18</v>
       </c>
+      <c r="I75" t="s">
+        <v>18</v>
+      </c>
+      <c r="J75" t="s">
+        <v>18</v>
+      </c>
+      <c r="K75" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
@@ -3406,6 +4072,15 @@
       <c r="H76" t="s">
         <v>18</v>
       </c>
+      <c r="I76" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" t="s">
+        <v>18</v>
+      </c>
+      <c r="K76" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -3432,6 +4107,15 @@
       <c r="H77" t="s">
         <v>18</v>
       </c>
+      <c r="I77" t="s">
+        <v>18</v>
+      </c>
+      <c r="J77" t="s">
+        <v>18</v>
+      </c>
+      <c r="K77" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -3458,6 +4142,15 @@
       <c r="H78" t="s">
         <v>18</v>
       </c>
+      <c r="I78" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" t="s">
+        <v>18</v>
+      </c>
+      <c r="K78" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
@@ -3484,6 +4177,15 @@
       <c r="H79" t="s">
         <v>18</v>
       </c>
+      <c r="I79" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" t="s">
+        <v>18</v>
+      </c>
+      <c r="K79" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
@@ -3510,6 +4212,15 @@
       <c r="H80" t="s">
         <v>18</v>
       </c>
+      <c r="I80" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" t="s">
+        <v>18</v>
+      </c>
+      <c r="K80" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
@@ -3536,6 +4247,15 @@
       <c r="H81" t="s">
         <v>18</v>
       </c>
+      <c r="I81" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" t="s">
+        <v>18</v>
+      </c>
+      <c r="K81" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
@@ -3562,6 +4282,15 @@
       <c r="H82" t="s">
         <v>18</v>
       </c>
+      <c r="I82" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" t="s">
+        <v>18</v>
+      </c>
+      <c r="K82" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
@@ -3588,6 +4317,15 @@
       <c r="H83" t="s">
         <v>18</v>
       </c>
+      <c r="I83" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" t="s">
+        <v>18</v>
+      </c>
+      <c r="K83" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -3614,6 +4352,15 @@
       <c r="H84" t="s">
         <v>18</v>
       </c>
+      <c r="I84" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" t="s">
+        <v>18</v>
+      </c>
+      <c r="K84" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
@@ -3640,6 +4387,15 @@
       <c r="H85" t="s">
         <v>18</v>
       </c>
+      <c r="I85" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" t="s">
+        <v>18</v>
+      </c>
+      <c r="K85" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -3666,6 +4422,15 @@
       <c r="H86" t="s">
         <v>18</v>
       </c>
+      <c r="I86" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" t="s">
+        <v>18</v>
+      </c>
+      <c r="K86" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
@@ -3692,6 +4457,15 @@
       <c r="H87" t="s">
         <v>18</v>
       </c>
+      <c r="I87" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" t="s">
+        <v>18</v>
+      </c>
+      <c r="K87" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
@@ -3718,6 +4492,15 @@
       <c r="H88" t="s">
         <v>18</v>
       </c>
+      <c r="I88" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" t="s">
+        <v>18</v>
+      </c>
+      <c r="K88" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
@@ -3744,6 +4527,15 @@
       <c r="H89" t="s">
         <v>18</v>
       </c>
+      <c r="I89" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" t="s">
+        <v>18</v>
+      </c>
+      <c r="K89" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
@@ -3770,6 +4562,15 @@
       <c r="H90" t="s">
         <v>18</v>
       </c>
+      <c r="I90" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" t="s">
+        <v>18</v>
+      </c>
+      <c r="K90" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
@@ -3796,6 +4597,15 @@
       <c r="H91" t="s">
         <v>18</v>
       </c>
+      <c r="I91" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" t="s">
+        <v>18</v>
+      </c>
+      <c r="K91" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -3822,6 +4632,15 @@
       <c r="H92" t="s">
         <v>18</v>
       </c>
+      <c r="I92" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" t="s">
+        <v>18</v>
+      </c>
+      <c r="K92" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
@@ -3848,6 +4667,15 @@
       <c r="H93" t="s">
         <v>18</v>
       </c>
+      <c r="I93" t="s">
+        <v>18</v>
+      </c>
+      <c r="J93" t="s">
+        <v>18</v>
+      </c>
+      <c r="K93" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -3874,6 +4702,15 @@
       <c r="H94" t="s">
         <v>18</v>
       </c>
+      <c r="I94" t="s">
+        <v>18</v>
+      </c>
+      <c r="J94" t="s">
+        <v>18</v>
+      </c>
+      <c r="K94" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -3900,6 +4737,15 @@
       <c r="H95" t="s">
         <v>18</v>
       </c>
+      <c r="I95" t="s">
+        <v>18</v>
+      </c>
+      <c r="J95" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
@@ -3926,6 +4772,15 @@
       <c r="H96" t="s">
         <v>18</v>
       </c>
+      <c r="I96" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -3952,6 +4807,15 @@
       <c r="H97" t="s">
         <v>18</v>
       </c>
+      <c r="I97" t="s">
+        <v>18</v>
+      </c>
+      <c r="J97" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
@@ -3978,6 +4842,15 @@
       <c r="H98" t="s">
         <v>18</v>
       </c>
+      <c r="I98" t="s">
+        <v>18</v>
+      </c>
+      <c r="J98" t="s">
+        <v>18</v>
+      </c>
+      <c r="K98" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -4004,6 +4877,15 @@
       <c r="H99" t="s">
         <v>18</v>
       </c>
+      <c r="I99" t="s">
+        <v>18</v>
+      </c>
+      <c r="J99" t="s">
+        <v>18</v>
+      </c>
+      <c r="K99" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
@@ -4030,6 +4912,15 @@
       <c r="H100" t="s">
         <v>18</v>
       </c>
+      <c r="I100" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
@@ -4056,6 +4947,15 @@
       <c r="H101" t="s">
         <v>18</v>
       </c>
+      <c r="I101" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" t="s">
+        <v>18</v>
+      </c>
+      <c r="K101" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
@@ -4082,6 +4982,15 @@
       <c r="H102" t="s">
         <v>18</v>
       </c>
+      <c r="I102" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" t="s">
+        <v>18</v>
+      </c>
+      <c r="K102" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
@@ -4108,6 +5017,15 @@
       <c r="H103" t="s">
         <v>18</v>
       </c>
+      <c r="I103" t="s">
+        <v>18</v>
+      </c>
+      <c r="J103" t="s">
+        <v>18</v>
+      </c>
+      <c r="K103" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
@@ -4134,6 +5052,15 @@
       <c r="H104" t="s">
         <v>18</v>
       </c>
+      <c r="I104" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" t="s">
+        <v>18</v>
+      </c>
+      <c r="K104" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
@@ -4160,6 +5087,15 @@
       <c r="H105" t="s">
         <v>18</v>
       </c>
+      <c r="I105" t="s">
+        <v>18</v>
+      </c>
+      <c r="J105" t="s">
+        <v>18</v>
+      </c>
+      <c r="K105" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
@@ -4186,6 +5122,15 @@
       <c r="H106" t="s">
         <v>18</v>
       </c>
+      <c r="I106" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" t="s">
+        <v>18</v>
+      </c>
+      <c r="K106" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
@@ -4212,6 +5157,15 @@
       <c r="H107" t="s">
         <v>18</v>
       </c>
+      <c r="I107" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" t="s">
+        <v>18</v>
+      </c>
+      <c r="K107" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
@@ -4238,6 +5192,15 @@
       <c r="H108" t="s">
         <v>18</v>
       </c>
+      <c r="I108" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" t="s">
+        <v>18</v>
+      </c>
+      <c r="K108" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
@@ -4264,6 +5227,15 @@
       <c r="H109" t="s">
         <v>18</v>
       </c>
+      <c r="I109" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -4290,6 +5262,15 @@
       <c r="H110" t="s">
         <v>18</v>
       </c>
+      <c r="I110" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
@@ -4316,6 +5297,15 @@
       <c r="H111" t="s">
         <v>18</v>
       </c>
+      <c r="I111" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
@@ -4342,6 +5332,15 @@
       <c r="H112" t="s">
         <v>18</v>
       </c>
+      <c r="I112" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" t="s">
+        <v>18</v>
+      </c>
+      <c r="K112" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
@@ -4368,6 +5367,15 @@
       <c r="H113" t="s">
         <v>18</v>
       </c>
+      <c r="I113" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" t="s">
+        <v>18</v>
+      </c>
+      <c r="K113" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
@@ -4394,6 +5402,15 @@
       <c r="H114" t="s">
         <v>18</v>
       </c>
+      <c r="I114" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" t="s">
+        <v>18</v>
+      </c>
+      <c r="K114" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
@@ -4420,6 +5437,15 @@
       <c r="H115" t="s">
         <v>18</v>
       </c>
+      <c r="I115" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" t="s">
+        <v>18</v>
+      </c>
+      <c r="K115" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
@@ -4446,6 +5472,15 @@
       <c r="H116" t="s">
         <v>18</v>
       </c>
+      <c r="I116" t="s">
+        <v>18</v>
+      </c>
+      <c r="J116" t="s">
+        <v>18</v>
+      </c>
+      <c r="K116" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
@@ -4472,6 +5507,15 @@
       <c r="H117" t="s">
         <v>18</v>
       </c>
+      <c r="I117" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" t="s">
+        <v>18</v>
+      </c>
+      <c r="K117" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
@@ -4498,6 +5542,15 @@
       <c r="H118" t="s">
         <v>18</v>
       </c>
+      <c r="I118" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -4524,6 +5577,15 @@
       <c r="H119" t="s">
         <v>18</v>
       </c>
+      <c r="I119" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
@@ -4550,6 +5612,15 @@
       <c r="H120" t="s">
         <v>18</v>
       </c>
+      <c r="I120" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -4576,6 +5647,15 @@
       <c r="H121" t="s">
         <v>18</v>
       </c>
+      <c r="I121" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
@@ -4602,6 +5682,15 @@
       <c r="H122" t="s">
         <v>18</v>
       </c>
+      <c r="I122" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
@@ -4628,6 +5717,15 @@
       <c r="H123" t="s">
         <v>18</v>
       </c>
+      <c r="I123" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
@@ -4654,6 +5752,15 @@
       <c r="H124" t="s">
         <v>18</v>
       </c>
+      <c r="I124" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
@@ -4680,6 +5787,15 @@
       <c r="H125" t="s">
         <v>18</v>
       </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
@@ -4706,6 +5822,15 @@
       <c r="H126" t="s">
         <v>18</v>
       </c>
+      <c r="I126" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
@@ -4732,6 +5857,15 @@
       <c r="H127" t="s">
         <v>18</v>
       </c>
+      <c r="I127" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" t="s">
+        <v>18</v>
+      </c>
+      <c r="K127" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
@@ -4758,6 +5892,15 @@
       <c r="H128" t="s">
         <v>18</v>
       </c>
+      <c r="I128" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" t="s">
+        <v>18</v>
+      </c>
+      <c r="K128" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
@@ -4784,6 +5927,15 @@
       <c r="H129" t="s">
         <v>18</v>
       </c>
+      <c r="I129" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" t="s">
+        <v>18</v>
+      </c>
+      <c r="K129" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
@@ -4810,6 +5962,15 @@
       <c r="H130" t="s">
         <v>18</v>
       </c>
+      <c r="I130" t="s">
+        <v>18</v>
+      </c>
+      <c r="J130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
@@ -4836,6 +5997,15 @@
       <c r="H131" t="s">
         <v>18</v>
       </c>
+      <c r="I131" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" t="s">
+        <v>18</v>
+      </c>
+      <c r="K131" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
@@ -4862,6 +6032,15 @@
       <c r="H132" t="s">
         <v>18</v>
       </c>
+      <c r="I132" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" t="s">
+        <v>18</v>
+      </c>
+      <c r="K132" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
@@ -4886,6 +6065,15 @@
         <v>28</v>
       </c>
       <c r="H133" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>18</v>
+      </c>
+      <c r="J133" t="s">
+        <v>18</v>
+      </c>
+      <c r="K133" t="s">
         <v>18</v>
       </c>
     </row>

--- a/downloads/receipts.xlsx
+++ b/downloads/receipts.xlsx
@@ -46,124 +46,124 @@
     <t>blob</t>
   </si>
   <si>
+    <t>txZONeYTGMhM</t>
+  </si>
+  <si>
+    <t>fi6DqtSpQQxB</t>
+  </si>
+  <si>
+    <t>dominos_Nov_05_2025.png</t>
+  </si>
+  <si>
+    <t>RECEIPT</t>
+  </si>
+  <si>
+    <t>image/png</t>
+  </si>
+  <si>
+    <t>usxGgLmlhGIn</t>
+  </si>
+  <si>
+    <t>ou3buQtZatb1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>txwCBf0vxiTB</t>
+  </si>
+  <si>
+    <t>fimbazDdoan6</t>
+  </si>
+  <si>
+    <t>amazon_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>txvD8YnSeMMb</t>
+  </si>
+  <si>
+    <t>fiQc4Ng1RRK8</t>
+  </si>
+  <si>
+    <t>marriott_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>txZDF9PjEj3o</t>
+  </si>
+  <si>
+    <t>fib4h01PgYUA</t>
+  </si>
+  <si>
+    <t>staples_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>tx6rtotdbaqd</t>
+  </si>
+  <si>
+    <t>fiWC95WYgH7K</t>
+  </si>
+  <si>
+    <t>extension.pdf</t>
+  </si>
+  <si>
+    <t>application/pdf</t>
+  </si>
+  <si>
+    <t>fiWlWI0d4RYo</t>
+  </si>
+  <si>
+    <t>taco_251116pf00802583_cd238f9d3d4b4f3aaeaa9ccf94e1eda9.pdf</t>
+  </si>
+  <si>
+    <t>txMDepeX0kkO</t>
+  </si>
+  <si>
+    <t>fiUAGZoUsr1n</t>
+  </si>
+  <si>
+    <t>lyft_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>txBKBOkRqvmR</t>
+  </si>
+  <si>
+    <t>fiaLtjj1hBH4</t>
+  </si>
+  <si>
+    <t>uber_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>tx3XbGNiTOTU</t>
+  </si>
+  <si>
+    <t>fi5n0m9PkGSn</t>
+  </si>
+  <si>
+    <t>dominos_Nov_25_2025.png</t>
+  </si>
+  <si>
     <t>txVnxp46ZpIu</t>
   </si>
   <si>
     <t>fipWgaI1P89R</t>
   </si>
   <si>
-    <t>lyft_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>RECEIPT</t>
-  </si>
-  <si>
-    <t>image/png</t>
-  </si>
-  <si>
     <t>usyXAERqjQGX</t>
   </si>
   <si>
     <t>ouHelfvTOEYt</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>txEmIYAmi2gA</t>
   </si>
   <si>
     <t>fiu43ggBqrX6</t>
   </si>
   <si>
-    <t>dominos_Nov_05_2025.png</t>
-  </si>
-  <si>
     <t>txRQU6y8eN1t</t>
   </si>
   <si>
     <t>fi6g9ZYnN9bk</t>
-  </si>
-  <si>
-    <t>dominos_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>txZONeYTGMhM</t>
-  </si>
-  <si>
-    <t>fi6DqtSpQQxB</t>
-  </si>
-  <si>
-    <t>usxGgLmlhGIn</t>
-  </si>
-  <si>
-    <t>ou3buQtZatb1</t>
-  </si>
-  <si>
-    <t>txwCBf0vxiTB</t>
-  </si>
-  <si>
-    <t>fimbazDdoan6</t>
-  </si>
-  <si>
-    <t>amazon_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>txvD8YnSeMMb</t>
-  </si>
-  <si>
-    <t>fiQc4Ng1RRK8</t>
-  </si>
-  <si>
-    <t>marriott_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>txZDF9PjEj3o</t>
-  </si>
-  <si>
-    <t>fib4h01PgYUA</t>
-  </si>
-  <si>
-    <t>staples_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>tx6rtotdbaqd</t>
-  </si>
-  <si>
-    <t>fiWC95WYgH7K</t>
-  </si>
-  <si>
-    <t>extension.pdf</t>
-  </si>
-  <si>
-    <t>application/pdf</t>
-  </si>
-  <si>
-    <t>fiWlWI0d4RYo</t>
-  </si>
-  <si>
-    <t>taco_251116pf00802583_cd238f9d3d4b4f3aaeaa9ccf94e1eda9.pdf</t>
-  </si>
-  <si>
-    <t>txMDepeX0kkO</t>
-  </si>
-  <si>
-    <t>fiUAGZoUsr1n</t>
-  </si>
-  <si>
-    <t>txBKBOkRqvmR</t>
-  </si>
-  <si>
-    <t>fiaLtjj1hBH4</t>
-  </si>
-  <si>
-    <t>uber_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>tx3XbGNiTOTU</t>
-  </si>
-  <si>
-    <t>fi5n0m9PkGSn</t>
   </si>
   <si>
     <t>txyL0yI2g8bT</t>
@@ -1570,7 +1570,7 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1579,10 +1579,10 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
@@ -1599,25 +1599,25 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -1634,25 +1634,25 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
         <v>32</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
@@ -1669,14 +1669,14 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
@@ -1684,10 +1684,10 @@
         <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
@@ -1704,25 +1704,25 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -1739,25 +1739,25 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
@@ -1774,25 +1774,25 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
         <v>44</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
@@ -1809,25 +1809,25 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s">
         <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" t="s">
-        <v>28</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
@@ -1850,7 +1850,7 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1859,10 +1859,10 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
@@ -1894,10 +1894,10 @@
         <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
@@ -1929,10 +1929,10 @@
         <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
@@ -1964,10 +1964,10 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
@@ -1999,10 +1999,10 @@
         <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
@@ -2034,10 +2034,10 @@
         <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
@@ -2069,10 +2069,10 @@
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
@@ -2104,10 +2104,10 @@
         <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
         <v>18</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
@@ -2174,10 +2174,10 @@
         <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
@@ -2209,10 +2209,10 @@
         <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
@@ -2244,10 +2244,10 @@
         <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
@@ -2279,10 +2279,10 @@
         <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
@@ -2314,10 +2314,10 @@
         <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
@@ -2349,10 +2349,10 @@
         <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
@@ -2384,10 +2384,10 @@
         <v>15</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
@@ -2419,10 +2419,10 @@
         <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
@@ -2454,10 +2454,10 @@
         <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
@@ -2489,10 +2489,10 @@
         <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
@@ -2524,10 +2524,10 @@
         <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
@@ -2559,10 +2559,10 @@
         <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
@@ -2594,10 +2594,10 @@
         <v>15</v>
       </c>
       <c r="F34" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
@@ -2629,10 +2629,10 @@
         <v>15</v>
       </c>
       <c r="F35" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
@@ -2664,10 +2664,10 @@
         <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
@@ -2699,10 +2699,10 @@
         <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
@@ -2734,10 +2734,10 @@
         <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
@@ -2769,10 +2769,10 @@
         <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
@@ -2804,10 +2804,10 @@
         <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
@@ -2839,10 +2839,10 @@
         <v>15</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
@@ -2874,10 +2874,10 @@
         <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
@@ -2909,10 +2909,10 @@
         <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
@@ -2944,10 +2944,10 @@
         <v>15</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
@@ -2979,10 +2979,10 @@
         <v>15</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
@@ -3014,10 +3014,10 @@
         <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
@@ -3049,10 +3049,10 @@
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
@@ -3084,10 +3084,10 @@
         <v>15</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
@@ -3119,10 +3119,10 @@
         <v>15</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
@@ -3154,10 +3154,10 @@
         <v>15</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
@@ -3189,10 +3189,10 @@
         <v>15</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
@@ -3224,10 +3224,10 @@
         <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
@@ -3259,10 +3259,10 @@
         <v>15</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -3294,10 +3294,10 @@
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
@@ -3329,10 +3329,10 @@
         <v>15</v>
       </c>
       <c r="F55" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
@@ -3364,10 +3364,10 @@
         <v>15</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
@@ -3399,10 +3399,10 @@
         <v>15</v>
       </c>
       <c r="F57" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
@@ -3434,10 +3434,10 @@
         <v>15</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -3469,10 +3469,10 @@
         <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -3504,10 +3504,10 @@
         <v>15</v>
       </c>
       <c r="F60" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
@@ -3530,19 +3530,19 @@
         <v>165</v>
       </c>
       <c r="C61" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D61" t="s">
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F61" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
@@ -3571,13 +3571,13 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F62" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
@@ -3609,10 +3609,10 @@
         <v>15</v>
       </c>
       <c r="F63" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -3644,10 +3644,10 @@
         <v>15</v>
       </c>
       <c r="F64" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
@@ -3679,10 +3679,10 @@
         <v>15</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G65" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
@@ -3714,10 +3714,10 @@
         <v>15</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G66" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
@@ -3749,10 +3749,10 @@
         <v>15</v>
       </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G67" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
@@ -3784,10 +3784,10 @@
         <v>15</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
@@ -3819,10 +3819,10 @@
         <v>15</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G69" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
@@ -3845,19 +3845,19 @@
         <v>190</v>
       </c>
       <c r="C70" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D70" t="s">
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G70" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
@@ -3886,13 +3886,13 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G71" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
@@ -3915,19 +3915,19 @@
         <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D72" t="s">
         <v>14</v>
       </c>
       <c r="E72" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G72" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
@@ -3956,13 +3956,13 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G73" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H73" t="s">
         <v>18</v>
@@ -3991,13 +3991,13 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F74" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
@@ -4020,19 +4020,19 @@
         <v>198</v>
       </c>
       <c r="C75" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D75" t="s">
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G75" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
@@ -4064,10 +4064,10 @@
         <v>15</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G76" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H76" t="s">
         <v>18</v>
@@ -4090,19 +4090,19 @@
         <v>203</v>
       </c>
       <c r="C77" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D77" t="s">
         <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
@@ -4131,13 +4131,13 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F78" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G78" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
@@ -4169,10 +4169,10 @@
         <v>15</v>
       </c>
       <c r="F79" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
@@ -4204,10 +4204,10 @@
         <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
@@ -4236,13 +4236,13 @@
         <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F81" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G81" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
@@ -4265,19 +4265,19 @@
         <v>214</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D82" t="s">
         <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F82" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
@@ -4309,10 +4309,10 @@
         <v>15</v>
       </c>
       <c r="F83" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
@@ -4344,10 +4344,10 @@
         <v>15</v>
       </c>
       <c r="F84" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
@@ -4379,10 +4379,10 @@
         <v>15</v>
       </c>
       <c r="F85" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
@@ -4414,10 +4414,10 @@
         <v>224</v>
       </c>
       <c r="F86" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G86" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s">
         <v>18</v>
@@ -4449,10 +4449,10 @@
         <v>15</v>
       </c>
       <c r="F87" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
@@ -4484,10 +4484,10 @@
         <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
@@ -4519,10 +4519,10 @@
         <v>15</v>
       </c>
       <c r="F89" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
@@ -4554,10 +4554,10 @@
         <v>224</v>
       </c>
       <c r="F90" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G90" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
@@ -4589,10 +4589,10 @@
         <v>15</v>
       </c>
       <c r="F91" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
@@ -4615,19 +4615,19 @@
         <v>240</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D92" t="s">
         <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F92" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
         <v>18</v>
@@ -4659,10 +4659,10 @@
         <v>15</v>
       </c>
       <c r="F93" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
@@ -4694,10 +4694,10 @@
         <v>15</v>
       </c>
       <c r="F94" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
@@ -4729,10 +4729,10 @@
         <v>15</v>
       </c>
       <c r="F95" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
@@ -4764,10 +4764,10 @@
         <v>15</v>
       </c>
       <c r="F96" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -4799,10 +4799,10 @@
         <v>15</v>
       </c>
       <c r="F97" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G97" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -4834,10 +4834,10 @@
         <v>15</v>
       </c>
       <c r="F98" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -4869,10 +4869,10 @@
         <v>15</v>
       </c>
       <c r="F99" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G99" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -4904,10 +4904,10 @@
         <v>15</v>
       </c>
       <c r="F100" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G100" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
@@ -4939,10 +4939,10 @@
         <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -4974,10 +4974,10 @@
         <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G102" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
@@ -5009,10 +5009,10 @@
         <v>15</v>
       </c>
       <c r="F103" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -5044,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="F104" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G104" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
@@ -5079,10 +5079,10 @@
         <v>15</v>
       </c>
       <c r="F105" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G105" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
@@ -5114,10 +5114,10 @@
         <v>15</v>
       </c>
       <c r="F106" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G106" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
@@ -5149,10 +5149,10 @@
         <v>15</v>
       </c>
       <c r="F107" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G107" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
@@ -5184,10 +5184,10 @@
         <v>15</v>
       </c>
       <c r="F108" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G108" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -5216,13 +5216,13 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F109" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G109" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -5245,19 +5245,19 @@
         <v>288</v>
       </c>
       <c r="C110" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D110" t="s">
         <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F110" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G110" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
@@ -5289,10 +5289,10 @@
         <v>15</v>
       </c>
       <c r="F111" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G111" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
@@ -5359,10 +5359,10 @@
         <v>15</v>
       </c>
       <c r="F113" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G113" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
@@ -5394,10 +5394,10 @@
         <v>15</v>
       </c>
       <c r="F114" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
@@ -5420,19 +5420,19 @@
         <v>302</v>
       </c>
       <c r="C115" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D115" t="s">
         <v>14</v>
       </c>
       <c r="E115" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F115" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G115" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
@@ -5464,10 +5464,10 @@
         <v>15</v>
       </c>
       <c r="F116" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G116" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
@@ -5499,10 +5499,10 @@
         <v>15</v>
       </c>
       <c r="F117" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G117" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
@@ -5534,10 +5534,10 @@
         <v>15</v>
       </c>
       <c r="F118" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G118" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
@@ -5569,10 +5569,10 @@
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G119" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
@@ -5604,10 +5604,10 @@
         <v>15</v>
       </c>
       <c r="F120" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G120" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -5639,10 +5639,10 @@
         <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G121" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
@@ -5674,10 +5674,10 @@
         <v>15</v>
       </c>
       <c r="F122" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G122" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
@@ -5709,10 +5709,10 @@
         <v>15</v>
       </c>
       <c r="F123" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -5744,10 +5744,10 @@
         <v>15</v>
       </c>
       <c r="F124" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G124" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
@@ -5779,10 +5779,10 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G125" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -5814,10 +5814,10 @@
         <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G126" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
@@ -5849,10 +5849,10 @@
         <v>15</v>
       </c>
       <c r="F127" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G127" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
@@ -5884,10 +5884,10 @@
         <v>15</v>
       </c>
       <c r="F128" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G128" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
@@ -5910,19 +5910,19 @@
         <v>334</v>
       </c>
       <c r="C129" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D129" t="s">
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F129" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G129" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
@@ -5954,10 +5954,10 @@
         <v>15</v>
       </c>
       <c r="F130" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G130" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
@@ -5989,10 +5989,10 @@
         <v>15</v>
       </c>
       <c r="F131" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G131" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
@@ -6024,10 +6024,10 @@
         <v>15</v>
       </c>
       <c r="F132" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G132" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -6059,10 +6059,10 @@
         <v>15</v>
       </c>
       <c r="F133" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G133" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
